--- a/templates/Material_Import_Template.xlsx
+++ b/templates/Material_Import_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jay/workspace/wboc-srm/outputs/material-import-template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jay/workspace/lab/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96828E82-7C71-6F46-A5E9-C5951F12C1EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3B1516-644F-D240-9494-8DC4484CA57F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6680" yWindow="3460" windowWidth="29400" windowHeight="17060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Materials" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Material Name</t>
   </si>
@@ -70,79 +70,6 @@
   <si>
     <t>Price Data Date</t>
   </si>
-  <si>
-    <t>PLC</t>
-  </si>
-  <si>
-    <t>CX7000</t>
-  </si>
-  <si>
-    <t>传动</t>
-  </si>
-  <si>
-    <t>电缸</t>
-  </si>
-  <si>
-    <t>PCS</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>MBYS/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F2937"/>
-        <rFont val="FangSong"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>美蓓亚斯</t>
-    </r>
-  </si>
-  <si>
-    <t>Processor Arm® Cortex®-M7, 480 MHz
-Number of cores 1
-Flash memory slot for microSD card, 512 MB included (optionally expandable)
-Main memory 32 MB SDR (not expandable)
-Number of inputs 8 multi-functional inputs (24 V DC)
-Number of outputs 4 multi-functional outputs (24 V DC, 0.5 A, 1-wire technique)
-NOVRAM 4 kB
-Interfaces 1 x RJ45 10/100 Mbit/s, 1 x USB
-Cooling passive
-Bus interface –
-Data transfer rates –
-Diagnostics LED 1 x TC status, 1 x WD, 1 x error, 1 x flash access
-Clock internal, capacitor-buffered real-time clock for time and date (storage capacity &gt; 21 days)
-Operating system TwinCAT/RTOS
-Control software TwinCAT 3 runtime (XAR)
-I/O connection E-bus or K-bus, automatic recognition
-Power supply 24 V (-15%/+20%)
-UPS OCT-capable no
-Current supply E-bus/K-bus 1.5 A
-Max. power consumption &lt; 2.0 W
-Max. power consumption E-bus/K-bus 7.5 W
-Dimensions (W x H x D) 49 mm x 100 mm x 73 mm
-Weight 142 g
-Operating temperature -25…+60°C
-Storage temperature -40…+85°C
-Relative humidity 95%, no condensation
-Vibration/shock resistance conforms to EN 60068-2-6/EN 60068-2-27
-EMC immunity/emission conforms to EN 61000-6-2/EN 61000-6-4
-Protection rating IP20
-Included TwinCAT 3 Function TC1000 TwinCAT 3 ADS, TC1100 TwinCAT 3 I/O, TC1200 TwinCAT 3 PLC, TF4100 TwinCAT 3 Controller Toolbox, TF4110 TwinCAT 3 Temperature Controller, TF6255 TwinCAT 3 Modbus RTU, TF6340 TwinCAT 3 Serial Communication, TF6701 TwinCAT 3 IoT Communication (MQTT), TF6730 TwinCAT 3 IoT Communicator, TF6760 TwinCAT 3 IoT HTTPS/REST
-Approvals/markings CE, UL
-TwinCAT 3 platform level Basic (10); please see here for an overview of all the TwinCAT 3 platform level</t>
-  </si>
-  <si>
-    <t>CNY</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>BYD</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
@@ -151,7 +78,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -174,27 +101,13 @@
       <name val="Carlito"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="FangSong"/>
       <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1F2937"/>
-      <name val="FangSong"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -206,14 +119,8 @@
         <fgColor rgb="FF1F2937"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -239,27 +146,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -282,15 +174,6 @@
     <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -310,8 +193,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MaterialImportTable" displayName="MaterialImportTable" ref="A1:L101" totalsRowShown="0">
-  <autoFilter ref="A1:L101" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="MaterialImportTable" displayName="MaterialImportTable" ref="A1:L100" totalsRowShown="0">
+  <autoFilter ref="A1:L100" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Material Name"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Manufacturer Part Number"/>
@@ -525,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -579,40 +462,18 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="22" customHeight="1">
-      <c r="A2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>15</v>
-      </c>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="4">
-        <v>100</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="6">
-        <v>46295</v>
-      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="6"/>
     </row>
     <row r="3" spans="1:12" ht="22" customHeight="1">
       <c r="A3" s="2"/>
@@ -1973,35 +1834,21 @@
       <c r="L99" s="6"/>
     </row>
     <row r="100" spans="1:12" ht="22" customHeight="1">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
-      <c r="I100" s="4"/>
-      <c r="J100" s="2"/>
-      <c r="K100" s="2"/>
-      <c r="L100" s="6"/>
-    </row>
-    <row r="101" spans="1:12" ht="22" customHeight="1">
-      <c r="A101" s="3"/>
-      <c r="B101" s="3"/>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3"/>
-      <c r="E101" s="3"/>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3"/>
-      <c r="H101" s="3"/>
-      <c r="I101" s="5"/>
-      <c r="J101" s="3"/>
-      <c r="K101" s="3"/>
-      <c r="L101" s="7"/>
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="5"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="3"/>
+      <c r="L100" s="7"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/templates/Material_Import_Template.xlsx
+++ b/templates/Material_Import_Template.xlsx
@@ -1,71 +1,113 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materials" sheetId="1" r:id="R69b6fdf20da54686"/>
-  </x:sheets>
-</x:workbook>
-</file>
-
-<file path=xl/metadata1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:metadata xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:metadataTypes count="1">
-    <x:metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </x:metadataTypes>
-  <x:futureMetadata name="XLDAPR" count="1">
-    <x:bk>
-      <x:extLst>
-        <x:ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" fDynamic="1" fCollapsed="0"/>
-        </x:ext>
-      </x:extLst>
-    </x:bk>
-  </x:futureMetadata>
-  <x:cellMetadata count="1">
-    <x:bk>
-      <x:rc t="1" v="0"/>
-    </x:bk>
-  </x:cellMetadata>
-</x:metadata>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <sheets>
+    <sheet name="Materials" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames/>
+</workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
-    <x:numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </x:numFmts>
-  <x:fonts count="1">
-    <x:font>
-      <x:sz val="12"/>
-      <x:color theme="1"/>
-      <x:name val="Calibri"/>
-    </x:font>
-  </x:fonts>
-  <x:fills count="2">
-    <x:fill>
-      <x:patternFill patternType="none"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="gray125"/>
-    </x:fill>
-  </x:fills>
-  <x:borders count="1">
-    <x:border/>
-  </x:borders>
-  <x:cellStyleXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </x:cellStyleXfs>
-  <x:cellXfs count="1">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-  </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0"/>
-  </x:cellStyles>
-</x:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
+    <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
+      <sz val="12"/>
+    </font>
+  </fonts>
+  <fills count="2">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border/>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0"/>
+  </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -277,105 +319,180 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" t="str">
-        <x:v>Material Name (English)</x:v>
-      </x:c>
-      <x:c r="B1" t="str">
-        <x:v>Material Name (Chinese)</x:v>
-      </x:c>
-      <x:c r="C1" t="str">
-        <x:v>Manufacturer Part Number</x:v>
-      </x:c>
-      <x:c r="D1" t="str">
-        <x:v>Category1</x:v>
-      </x:c>
-      <x:c r="E1" t="str">
-        <x:v>Category2</x:v>
-      </x:c>
-      <x:c r="F1" t="str">
-        <x:v>Category3</x:v>
-      </x:c>
-      <x:c r="G1" t="str">
-        <x:v>Unit</x:v>
-      </x:c>
-      <x:c r="H1" t="str">
-        <x:v>Brand</x:v>
-      </x:c>
-      <x:c r="I1" t="str">
-        <x:v>Description</x:v>
-      </x:c>
-      <x:c r="J1" t="str">
-        <x:v>Reference Price</x:v>
-      </x:c>
-      <x:c r="K1" t="str">
-        <x:v>Currency</x:v>
-      </x:c>
-      <x:c r="L1" t="str">
-        <x:v>Price Source</x:v>
-      </x:c>
-      <x:c r="M1" t="str">
-        <x:v>Price Data Date</x:v>
-      </x:c>
-      <x:c r="N1" t="str">
-        <x:v>Image URL</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="str">
-        <x:v>Oak Panel</x:v>
-      </x:c>
-      <x:c r="B2" t="str">
-        <x:v>橡木板</x:v>
-      </x:c>
-      <x:c r="C2" t="str">
-        <x:v>MPN-12345</x:v>
-      </x:c>
-      <x:c r="D2" t="str">
-        <x:v>Wood</x:v>
-      </x:c>
-      <x:c r="E2" t="str">
-        <x:v>Panels</x:v>
-      </x:c>
-      <x:c r="F2" t="str">
-        <x:v>Oak</x:v>
-      </x:c>
-      <x:c r="G2" t="str">
-        <x:v>PCS</x:v>
-      </x:c>
-      <x:c r="H2" t="str">
-        <x:v>Acme</x:v>
-      </x:c>
-      <x:c r="I2" t="str">
-        <x:v>Solid oak panel, 18mm thickness</x:v>
-      </x:c>
-      <x:c r="J2" t="str">
-        <x:v>350.00</x:v>
-      </x:c>
-      <x:c r="K2" t="str">
-        <x:v>CNY</x:v>
-      </x:c>
-      <x:c r="L2" t="str">
-        <x:v>Supplier Quote</x:v>
-      </x:c>
-      <x:c r="M2" t="str">
-        <x:v>2026-01-15</x:v>
-      </x:c>
-      <x:c r="N2" t="str">
-        <x:v>https://example.com/images/oak-panel.jpg</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:dataValidations count="2">
-    <x:dataValidation type="list" sqref="G2:G5001">
-      <x:formula1>"EACH,PIECE,DEVICE,SET,COUNT,BOX,PACK,BAG,BOTTLE,BARREL,METER,SQUARE_METER,CUBIC_METER,KILOGRAM,GRAM,TONNE,LITER,MILLILITER,SHEET,ROLL,PCS"</x:formula1>
-    </x:dataValidation>
-    <x:dataValidation type="list" sqref="K2:K5001">
-      <x:formula1>"CNY,USD,EUR,GBP"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Material Name (English)</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Material Name (Chinese)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Manufacturer Part Number</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Category1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Category2</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Category3</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Reference Price</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Price Source</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Price Data Date</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Incoterms</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Image URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Oak Panel</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>橡木板</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MPN-12345</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Panels</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Oak</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PCS</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Acme</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Solid oak panel, 18mm thickness</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>350.00</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Supplier Quote</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>FOB</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>https://example.com/images/oak-panel.jpg</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="G2:G5001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"EACH,PIECE,DEVICE,SET,COUNT,BOX,PACK,BAG,BOTTLE,BARREL,METER,SQUARE_METER,CUBIC_METER,KILOGRAM,GRAM,TONNE,LITER,MILLILITER,SHEET,ROLL,PCS"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K5001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"CNY,USD,EUR,GBP"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N5001" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"EXW,FOB,CIF,DDP,DAP"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>